--- a/models/Cimko_Cimento_Credit_Model.xlsx
+++ b/models/Cimko_Cimento_Credit_Model.xlsx
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>3Q26</t>
+          <t>Q3 2026 / 9M</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>15:00 Istanbul / 12:00 UK</t>
+          <t>14:00 Local / Pre-Market</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C35" s="38" t="inlineStr">
         <is>
-          <t>https://www.cimko.com.tr/investor-relations</t>
+          <t>https://www.google.com/finance/quote/CIMKOC</t>
         </is>
       </c>
     </row>
